--- a/data/trans_orig/P1417-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2007</t>
+          <t>Población con diagnóstico de anemia en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489310</t>
+          <t>489389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463353</t>
+          <t>462904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955989</t>
+          <t>955085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730464</t>
+          <t>730444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608978</t>
+          <t>608204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>621186</t>
+          <t>620731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1342762</t>
+          <t>1343342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355962</t>
+          <t>1355728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633982</t>
+          <t>634232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668305</t>
+          <t>668198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683288</t>
+          <t>683343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306361</t>
+          <t>1305744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321491</t>
+          <t>1321426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513639</t>
+          <t>513613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502302</t>
+          <t>502976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512741</t>
+          <t>512754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1018827</t>
+          <t>1019483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1030158</t>
+          <t>1030992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387378</t>
+          <t>387126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399854</t>
+          <t>399856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>773265</t>
+          <t>774277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>785758</t>
+          <t>786573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281226</t>
+          <t>281263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290967</t>
+          <t>291638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330026</t>
+          <t>329867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340162</t>
+          <t>340052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616138</t>
+          <t>616088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>629433</t>
+          <t>630035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198628</t>
+          <t>197735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208841</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312100</t>
+          <t>310991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>327105</t>
+          <t>327087</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>516761</t>
+          <t>515737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533360</t>
+          <t>533672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73613</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3253841</t>
+          <t>3254465</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3269786</t>
+          <t>3269199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3305584</t>
+          <t>3305020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3335927</t>
+          <t>3335588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6565780</t>
+          <t>6565794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6599602</t>
+          <t>6601654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2012</t>
+          <t>Población con diagnóstico de anemia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420597</t>
+          <t>420615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429266</t>
+          <t>429258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875120</t>
+          <t>874689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883405</t>
+          <t>883326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>682248</t>
+          <t>681714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>590329</t>
+          <t>590667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604421</t>
+          <t>605099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1275335</t>
+          <t>1276734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1291017</t>
+          <t>1291302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676472</t>
+          <t>675619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669094</t>
+          <t>669666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690518</t>
+          <t>690897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1349435</t>
+          <t>1349261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1371859</t>
+          <t>1370512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>25779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31743</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606075</t>
+          <t>605113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613654</t>
+          <t>613646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>586820</t>
+          <t>587438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604444</t>
+          <t>603866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1196091</t>
+          <t>1199363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216136</t>
+          <t>1216375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422295</t>
+          <t>422425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428380</t>
+          <t>428930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441536</t>
+          <t>441640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>853887</t>
+          <t>854465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869164</t>
+          <t>870011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>26790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296524</t>
+          <t>296623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307682</t>
+          <t>306868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334556</t>
+          <t>334689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349047</t>
+          <t>349049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>636984</t>
+          <t>636992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654152</t>
+          <t>653854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243438</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363726</t>
+          <t>364506</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>380241</t>
+          <t>380239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>611572</t>
+          <t>610801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628915</t>
+          <t>628724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119082</t>
+          <t>118642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3402132</t>
+          <t>3403317</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3418516</t>
+          <t>3417749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3434970</t>
+          <t>3435410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3475702</t>
+          <t>3476253</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6844194</t>
+          <t>6848596</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6888647</t>
+          <t>6891216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2016</t>
+          <t>Población con diagnóstico de anemia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412469</t>
+          <t>413398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384117</t>
+          <t>383942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393878</t>
+          <t>393782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>800987</t>
+          <t>799731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811427</t>
+          <t>811910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,77 +7054,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10763</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18802</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10763</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5748</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18315</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>11780</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>6756</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>19549</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>11780</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5965</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>19819</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584945</t>
+          <t>586370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,82 +7162,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>552781</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>544742</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>558235</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>552781</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>545229</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>557796</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1142260</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1134491</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1147284</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1142260</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1134221</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1148075</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661253</t>
+          <t>661161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638605</t>
+          <t>638187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652974</t>
+          <t>653220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303690</t>
+          <t>1305417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321271</t>
+          <t>1321255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27780</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637760</t>
+          <t>636758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>645043</t>
+          <t>645048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626171</t>
+          <t>624305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641631</t>
+          <t>641575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267345</t>
+          <t>1267836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285106</t>
+          <t>1284710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22192</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471462</t>
+          <t>470421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474657</t>
+          <t>474862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490215</t>
+          <t>490666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950471</t>
+          <t>949439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>966931</t>
+          <t>966635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323512</t>
+          <t>324134</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332444</t>
+          <t>333295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>358242</t>
+          <t>359055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>371679</t>
+          <t>371777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686061</t>
+          <t>685750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>702105</t>
+          <t>702760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247629</t>
+          <t>247160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255326</t>
+          <t>255406</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371650</t>
+          <t>371418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>389960</t>
+          <t>390074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623874</t>
+          <t>623766</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>643354</t>
+          <t>643585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70053</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>107871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>130168</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3364065</t>
+          <t>3364774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3382294</t>
+          <t>3382214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3434365</t>
+          <t>3436671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3474489</t>
+          <t>3474328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6812471</t>
+          <t>6808724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6853588</t>
+          <t>6851021</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2023</t>
+          <t>Población con diagnóstico de anemia en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281103</t>
+          <t>286569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>311005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>683909</t>
+          <t>685259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711046</t>
+          <t>710992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490746</t>
+          <t>491234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506740</t>
+          <t>506488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915064</t>
+          <t>915212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929753</t>
+          <t>929919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40614</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47219</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521563</t>
+          <t>523838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534121</t>
+          <t>534222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501185</t>
+          <t>501428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518774</t>
+          <t>519112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030918</t>
+          <t>1030811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1051553</t>
+          <t>1050789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53904</t>
+          <t>54870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878446</t>
+          <t>878258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886026</t>
+          <t>886022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>663703</t>
+          <t>664559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683335</t>
+          <t>684465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1545068</t>
+          <t>1544102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1574713</t>
+          <t>1574737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544939</t>
+          <t>544631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555319</t>
+          <t>555196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522126</t>
+          <t>522743</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534198</t>
+          <t>533764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071683</t>
+          <t>1071631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1087258</t>
+          <t>1087149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>351057</t>
+          <t>350988</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361102</t>
+          <t>361291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>583968</t>
+          <t>584831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602353</t>
+          <t>602523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940819</t>
+          <t>940699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964539</t>
+          <t>961923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263828</t>
+          <t>263687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273953</t>
+          <t>273731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379982</t>
+          <t>380197</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395790</t>
+          <t>396080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>647655</t>
+          <t>647185</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>667011</t>
+          <t>666780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179045</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161067</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3403629</t>
+          <t>3404626</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3426763</t>
+          <t>3428124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3475149</t>
+          <t>3473708</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529770</t>
+          <t>3529567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6887884</t>
+          <t>6889066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6947936</t>
+          <t>6943988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1417-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489389</t>
+          <t>489313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462904</t>
+          <t>462495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955085</t>
+          <t>955105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730444</t>
+          <t>730436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608204</t>
+          <t>607664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620731</t>
+          <t>621353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1343342</t>
+          <t>1342872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355728</t>
+          <t>1355970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634232</t>
+          <t>633320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668198</t>
+          <t>667782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683343</t>
+          <t>683740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1304848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321426</t>
+          <t>1320865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513613</t>
+          <t>512714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502976</t>
+          <t>502050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512754</t>
+          <t>512735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1019483</t>
+          <t>1018985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1030992</t>
+          <t>1030128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387126</t>
+          <t>387644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399856</t>
+          <t>399811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774277</t>
+          <t>773914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786573</t>
+          <t>786499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281263</t>
+          <t>280687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291638</t>
+          <t>290991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329867</t>
+          <t>329265</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340052</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616088</t>
+          <t>616365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>630035</t>
+          <t>630218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197735</t>
+          <t>197975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>208838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310991</t>
+          <t>312147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>327087</t>
+          <t>327145</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515737</t>
+          <t>515810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533672</t>
+          <t>533823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3254465</t>
+          <t>3254200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3269199</t>
+          <t>3269219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3305020</t>
+          <t>3304197</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3335588</t>
+          <t>3335466</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6565794</t>
+          <t>6566375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6601654</t>
+          <t>6601682</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420615</t>
+          <t>420735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429258</t>
+          <t>429219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874689</t>
+          <t>874492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883326</t>
+          <t>883390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681714</t>
+          <t>681722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>590667</t>
+          <t>590518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605099</t>
+          <t>604533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1276734</t>
+          <t>1276251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1291302</t>
+          <t>1291364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20925</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42176</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675619</t>
+          <t>674889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669666</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690897</t>
+          <t>690269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1349261</t>
+          <t>1350905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1370512</t>
+          <t>1371111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,77 +4761,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15905</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8479</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>19014</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>10858</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>29912</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15905</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9351</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25779</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>19014</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>11459</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>28471</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>605113</t>
+          <t>606142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613646</t>
+          <t>613663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,82 +4869,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>597312</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>588349</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>604738</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1208820</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1197922</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1216976</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,45%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>597312</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>587438</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>603866</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1208820</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1199363</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1216375</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422425</t>
+          <t>422350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428930</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>441619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>854465</t>
+          <t>854005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870011</t>
+          <t>869823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296623</t>
+          <t>296378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306868</t>
+          <t>307699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334689</t>
+          <t>334536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349049</t>
+          <t>348057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>636992</t>
+          <t>635786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653854</t>
+          <t>653904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242998</t>
+          <t>242509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364506</t>
+          <t>362509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>380239</t>
+          <t>380099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610801</t>
+          <t>609166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628724</t>
+          <t>628007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>117794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132235</t>
+          <t>137955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3403317</t>
+          <t>3402307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3417749</t>
+          <t>3418477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3435410</t>
+          <t>3436258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3476253</t>
+          <t>3475097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6848596</t>
+          <t>6842876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6891216</t>
+          <t>6886560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413398</t>
+          <t>412261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383942</t>
+          <t>383081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393782</t>
+          <t>393771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>799731</t>
+          <t>799866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811910</t>
+          <t>811416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586370</t>
+          <t>585392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>544742</t>
+          <t>544695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>558235</t>
+          <t>557730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134491</t>
+          <t>1133477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1147284</t>
+          <t>1148150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,42 +7397,42 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14225</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7878</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22280</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14225</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8166</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23199</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>25459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661161</t>
+          <t>660473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,49 +7505,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>647161</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>639106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>653508</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>98,81%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>647161</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>638187</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>653220</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1287</t>
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305417</t>
+          <t>1305024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321255</t>
+          <t>1320693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636758</t>
+          <t>636775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>645048</t>
+          <t>646048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>624305</t>
+          <t>624804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641575</t>
+          <t>641549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267836</t>
+          <t>1267073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284710</t>
+          <t>1284582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470421</t>
+          <t>470318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474862</t>
+          <t>474645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490666</t>
+          <t>490097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>949439</t>
+          <t>949180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>966635</t>
+          <t>966289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>25929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324134</t>
+          <t>323810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333295</t>
+          <t>332453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359055</t>
+          <t>357651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>371777</t>
+          <t>371668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>685750</t>
+          <t>686163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>702760</t>
+          <t>701973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247160</t>
+          <t>247613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255406</t>
+          <t>255413</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371418</t>
+          <t>372844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>390074</t>
+          <t>389948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623766</t>
+          <t>623680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>643585</t>
+          <t>643546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70214</t>
+          <t>68985</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>106283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87871</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3364774</t>
+          <t>3363859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3382214</t>
+          <t>3382288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3436671</t>
+          <t>3438259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3474328</t>
+          <t>3475557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6808724</t>
+          <t>6810459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6851021</t>
+          <t>6851604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>304032</t>
+          <t>352981</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286569</t>
+          <t>338922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311005</t>
+          <t>359619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>704019</t>
+          <t>760774</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685259</t>
+          <t>748568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710992</t>
+          <t>768071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500442</t>
+          <t>489788</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491234</t>
+          <t>480737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506488</t>
+          <t>495220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>923989</t>
+          <t>966678</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915212</t>
+          <t>959149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929919</t>
+          <t>972256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,17 +10421,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>41499</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>52827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>530711</t>
+          <t>615098</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523838</t>
+          <t>608447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534222</t>
+          <t>618809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511384</t>
+          <t>585729</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501428</t>
+          <t>573931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>519112</t>
+          <t>593966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1042095</t>
+          <t>1200826</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030811</t>
+          <t>1189498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1050789</t>
+          <t>1211631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>59054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>883719</t>
+          <t>695581</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878258</t>
+          <t>690620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886022</t>
+          <t>698458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>674237</t>
+          <t>694390</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>664559</t>
+          <t>683736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684465</t>
+          <t>703577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1557957</t>
+          <t>1389971</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1544102</t>
+          <t>1376725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1574737</t>
+          <t>1399439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886473</t>
+          <t>699284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886473</t>
+          <t>699284</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886473</t>
+          <t>699284</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598972</t>
+          <t>1435779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598972</t>
+          <t>1435779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598972</t>
+          <t>1435779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>34906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>551369</t>
+          <t>597635</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544631</t>
+          <t>590384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555196</t>
+          <t>601825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>529064</t>
+          <t>589767</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522743</t>
+          <t>581184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533764</t>
+          <t>595015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1080432</t>
+          <t>1187400</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071631</t>
+          <t>1178525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1087149</t>
+          <t>1194889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559352</t>
+          <t>607351</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559352</t>
+          <t>607351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559352</t>
+          <t>607351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543614</t>
+          <t>606081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543614</t>
+          <t>606081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543614</t>
+          <t>606081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102965</t>
+          <t>1213431</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102965</t>
+          <t>1213431</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102965</t>
+          <t>1213431</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>357082</t>
+          <t>395146</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350988</t>
+          <t>388553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361291</t>
+          <t>399565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>593561</t>
+          <t>423268</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584831</t>
+          <t>417314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602523</t>
+          <t>427949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>950643</t>
+          <t>818414</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>940699</t>
+          <t>810436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>961923</t>
+          <t>824779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606641</t>
+          <t>437252</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606641</t>
+          <t>437252</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606641</t>
+          <t>437252</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974088</t>
+          <t>843463</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974088</t>
+          <t>843463</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974088</t>
+          <t>843463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>49312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>48573</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39823</t>
+          <t>42893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59418</t>
+          <t>65524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>269631</t>
+          <t>295302</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263687</t>
+          <t>288841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273731</t>
+          <t>299961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>388399</t>
+          <t>424186</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380197</t>
+          <t>414369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396080</t>
+          <t>432182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>658030</t>
+          <t>719488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>647185</t>
+          <t>706988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>666780</t>
+          <t>729619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281665</t>
+          <t>308831</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281665</t>
+          <t>308831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281665</t>
+          <t>308831</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>463681</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>463681</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>463681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706603</t>
+          <t>772512</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706603</t>
+          <t>772512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706603</t>
+          <t>772512</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124627</t>
+          <t>146499</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180486</t>
+          <t>189643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>165015</t>
+          <t>189004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219937</t>
+          <t>238462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3416046</t>
+          <t>3483444</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3404626</t>
+          <t>3470100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3428124</t>
+          <t>3493098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3501120</t>
+          <t>3560108</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3473708</t>
+          <t>3538949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529567</t>
+          <t>3582093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6917166</t>
+          <t>7043553</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6889066</t>
+          <t>7017327</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6943988</t>
+          <t>7066785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
